--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -1,35 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quality" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Support" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Team" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Roles" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SLA" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Servers" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fundamentals" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Schema stg_customers" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Relationships" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Quality" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Support" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Team" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Roles" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="SLA" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Servers" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Pricing" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Custom Properties" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="DET Models" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="DET Model Inputs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="DET Sources" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="DET Source Schema" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="DET Mapping" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="DET Parameters" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="DET Relationships" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="Operational Validation" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="Operational Parameters" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="DET Lookups" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="DET Build" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="_DET Lists" sheetId="24" state="veryHidden" r:id="rId24"/>
+    <sheet name="_DET Metadata" sheetId="25" state="veryHidden" r:id="rId25"/>
+    <sheet name="_DET Context" sheetId="26" state="veryHidden" r:id="rId26"/>
+    <sheet name="_DET Raw ODCS" sheetId="27" state="veryHidden" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="apiVersion">Fundamentals!$C$5</definedName>
@@ -15591,7 +15591,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="161" min="1" max="1"/>
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>2.3.0</t>
+          <t>3.0.2</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>2.3.0</t>
+          <t>3.0.2</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>2.3.0</t>
+          <t>3.0.2</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1429ce4f80e5f9adf552a3fd404d94b7e7a0cd98434fff6fafe63717a8a6b8cf</t>
+          <t>63d2b950ce8bbc71970b53ea88f565f4b1316accc4ff288ace05532edfc75182</t>
         </is>
       </c>
     </row>
@@ -15684,6 +15684,10 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12"/>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="CCB4"/>
   <mergeCells count="2">
@@ -15906,11 +15910,15 @@
           <t>_det_invocation_id</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Remove Prefix</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Precision</t>
@@ -15926,6 +15934,8 @@
           <t>Trim</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Lookup</t>
@@ -15956,21 +15966,29 @@
           <t>Allow Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr">
         <is>
           <t>Lookup</t>
         </is>
       </c>
+      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
           <t>Pattern</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr">
         <is>
           <t>Operator</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
       <c r="AE2" t="inlineStr">
         <is>
           <t>customer_id</t>
@@ -20600,7 +20618,16 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="15">
+  <dataValidations count="18">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.2</t>
+          <t>3.0.3</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>63d2b950ce8bbc71970b53ea88f565f4b1316accc4ff288ace05532edfc75182</t>
+          <t>bf4c150acbff83880b41db78850d5e09436aa99c889805695f1d7a8a2b90bbeb</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="18">
+  <dataValidations count="19">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.3</t>
+          <t>3.0.4</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.3</t>
+          <t>3.0.4</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.3</t>
+          <t>3.0.4</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bf4c150acbff83880b41db78850d5e09436aa99c889805695f1d7a8a2b90bbeb</t>
+          <t>ac3ea59527188645c7771fc723c3cb1676c83b06370a8318092dc82bdee5ddcd</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,13 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="19">
+  <dataValidations count="21">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.4</t>
+          <t>3.0.5</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.4</t>
+          <t>3.0.5</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.4</t>
+          <t>3.0.5</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ac3ea59527188645c7771fc723c3cb1676c83b06370a8318092dc82bdee5ddcd</t>
+          <t>80864bd3c138d9b186867baa0b5789dbe2f5aecacac3e1882fb0214611f059c6</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="21">
+  <dataValidations count="22">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v2.3.0</t>
+          <t>v3.0.5</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="23">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v3.0.5</t>
+          <t>v3.0.6</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.5</t>
+          <t>3.0.6</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.5</t>
+          <t>3.0.6</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.5</t>
+          <t>3.0.6</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80864bd3c138d9b186867baa0b5789dbe2f5aecacac3e1882fb0214611f059c6</t>
+          <t>3385d149ed874f52ab9eaebff1fcea94dbdf2bf04554c8714bbee079d7b75cc1</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="23">
+  <dataValidations count="24">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -20618,7 +20618,13 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="24">
+  <dataValidations count="26">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v3.0.6</t>
+          <t>v3.0.7</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.6</t>
+          <t>3.0.7</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.6</t>
+          <t>3.0.7</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.6</t>
+          <t>3.0.7</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3385d149ed874f52ab9eaebff1fcea94dbdf2bf04554c8714bbee079d7b75cc1</t>
+          <t>41642ef65d27f48c1c1afa0d28cbede1d4dab293fa38f8cc3d63d2c842a506b1</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="26">
+  <dataValidations count="27">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v3.0.7</t>
+          <t>v3.1.0</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.0.7</t>
+          <t>3.1.0</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.0.7</t>
+          <t>3.1.0</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.0.7</t>
+          <t>3.1.0</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41642ef65d27f48c1c1afa0d28cbede1d4dab293fa38f8cc3d63d2c842a506b1</t>
+          <t>9ae914bf42d345285c3985b0de3b6b64508eaf8096bb35b16913fcd190856139</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="27">
+  <dataValidations count="28">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v3.1.0</t>
+          <t>v3.2.0</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.2.0</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.2.0</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.1.0</t>
+          <t>3.2.0</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9ae914bf42d345285c3985b0de3b6b64508eaf8096bb35b16913fcd190856139</t>
+          <t>10692e8a36e7534e55aa189aae4dcd8b67a9dea29bddd266458e1805bbe6a292</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="28">
+  <dataValidations count="29">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v3.2.0</t>
+          <t>v4.0.0</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>3.2.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>3.2.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>3.2.0</t>
+          <t>4.0.0</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10692e8a36e7534e55aa189aae4dcd8b67a9dea29bddd266458e1805bbe6a292</t>
+          <t>fea1df4290a6aaca375bf5aa893b60143711eecf058837ea9966781ccdfec370</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="29">
+  <dataValidations count="30">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v4.0.0</t>
+          <t>v4.0.1</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>4.0.1</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>4.0.1</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>4.0.0</t>
+          <t>4.0.1</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fea1df4290a6aaca375bf5aa893b60143711eecf058837ea9966781ccdfec370</t>
+          <t>e2acfc2e0890bcdab4dff026b45d0a7cb829264b7740d6c5a3a294ed19838491</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="30">
+  <dataValidations count="31">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -1637,7 +1637,7 @@
     <row r="31" ht="16" customHeight="1" s="161">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v2.3.0 workflow</t>
+          <t>dbt_data_engineering_toolkit v4.0.2 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v4.0.1</t>
+          <t>v4.0.2</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>4.0.2</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>4.0.2</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>4.0.1</t>
+          <t>4.0.2</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>e2acfc2e0890bcdab4dff026b45d0a7cb829264b7740d6c5a3a294ed19838491</t>
+          <t>066d9de11044f7150f776fde702a85e80b973ff3f1dd0b222143d33d263f6cd3</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="31">
+  <dataValidations count="32">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -1637,7 +1637,7 @@
     <row r="31" ht="16" customHeight="1" s="161">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v4.0.2 workflow</t>
+          <t>dbt_data_engineering_toolkit v4.0.3 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -1826,17 +1826,17 @@
       </c>
       <c r="B40" s="51" t="inlineStr">
         <is>
-          <t>Generate, sync, and lint</t>
+          <t>Export package env var, then generate, sync, and lint</t>
         </is>
       </c>
       <c r="C40" s="51" t="inlineStr">
         <is>
-          <t>Post-sync ODCS + dbt + SQLFluff</t>
+          <t>dbt package refs resolve from your published toolkit Git URL</t>
         </is>
       </c>
       <c r="D40" s="51" t="inlineStr">
         <is>
-          <t>det generate ...; dbt deps; det check ...</t>
+          <t>export DBT_DATA_ENGINEERING_TOOLKIT_GIT_URL=https://github.com/systemizing-solutions/dbt_data_engineering_toolkit.git; det generate ...; dbt deps; det check ...</t>
         </is>
       </c>
     </row>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v4.0.2</t>
+          <t>v4.0.3</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>4.0.2</t>
+          <t>4.0.3</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>4.0.2</t>
+          <t>4.0.3</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>4.0.2</t>
+          <t>4.0.3</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>066d9de11044f7150f776fde702a85e80b973ff3f1dd0b222143d33d263f6cd3</t>
+          <t>9bd2f400c5672aff5aedd6e0dba3b965891004b13ebe15eaae9fc77a6d321a88</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="32">
+  <dataValidations count="33">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -1637,7 +1637,7 @@
     <row r="31" ht="16" customHeight="1" s="161">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v4.0.3 workflow</t>
+          <t>dbt_data_engineering_toolkit v4.1.0 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v4.0.3</t>
+          <t>v4.1.0</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>4.0.3</t>
+          <t>4.1.0</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>4.0.3</t>
+          <t>4.1.0</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>4.0.3</t>
+          <t>4.1.0</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>9bd2f400c5672aff5aedd6e0dba3b965891004b13ebe15eaae9fc77a6d321a88</t>
+          <t>f320cb1d12b94278a63e1b1b74766e43ffaeb001f718b0e155ceae6a8015d083</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="33">
+  <dataValidations count="34">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>

--- a/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
+++ b/python/src/dbt_data_engineering_toolkit_compiler/resources/data_product_sample.xlsx
@@ -1637,7 +1637,7 @@
     <row r="31" ht="16" customHeight="1" s="161">
       <c r="A31" s="44" t="inlineStr">
         <is>
-          <t>dbt_data_engineering_toolkit v4.1.0 workflow</t>
+          <t>dbt_data_engineering_toolkit v4.1.1 workflow</t>
         </is>
       </c>
       <c r="E31" s="13" t="n"/>
@@ -14561,7 +14561,7 @@
       </c>
       <c r="B8" s="179" t="inlineStr">
         <is>
-          <t>v4.1.0</t>
+          <t>v4.1.1</t>
         </is>
       </c>
       <c r="C8" s="165" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="B4" s="165" t="inlineStr">
         <is>
-          <t>4.1.0</t>
+          <t>4.1.1</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15644,7 @@
       </c>
       <c r="B5" s="165" t="inlineStr">
         <is>
-          <t>4.1.0</t>
+          <t>4.1.1</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15656,7 @@
       </c>
       <c r="B6" s="165" t="inlineStr">
         <is>
-          <t>4.1.0</t>
+          <t>4.1.1</t>
         </is>
       </c>
     </row>
@@ -15668,7 +15668,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>f320cb1d12b94278a63e1b1b74766e43ffaeb001f718b0e155ceae6a8015d083</t>
+          <t>8ce22f79a05d82b337ecfe7087086e2cd216b3f3c9bbeea134d8e716bac4aaf5</t>
         </is>
       </c>
     </row>
@@ -20618,7 +20618,10 @@
     <mergeCell ref="B5:E5"/>
     <mergeCell ref="B10:E10"/>
   </mergeCells>
-  <dataValidations count="34">
+  <dataValidations count="35">
+    <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
+      <formula1>'_DET Lists'!$U$2:$U$4</formula1>
+    </dataValidation>
     <dataValidation sqref="AM14:AM100" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Unsupported value" error="Choose a value from the controlled list." promptTitle="Controlled input" prompt="Select a supported value." type="list">
       <formula1>'_DET Lists'!$U$2:$U$4</formula1>
     </dataValidation>
